--- a/excel/role.xlsx
+++ b/excel/role.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12360"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -121,10 +121,10 @@
     <t>initiativeDesc</t>
   </si>
   <si>
-    <t>string</t>
+    <t>int</t>
   </si>
   <si>
-    <t>int</t>
+    <t>string</t>
   </si>
   <si>
     <t>突击1</t>
@@ -1250,43 +1250,43 @@
         <v>28</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="E3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="K3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:14">

--- a/excel/role.xlsx
+++ b/excel/role.xlsx
@@ -32,6 +32,41 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+0：突进
+1：治疗
+2：肉盾
+3：功能</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -179,7 +214,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -336,6 +371,17 @@
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -4997,5 +5043,6 @@
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/excel/role.xlsx
+++ b/excel/role.xlsx
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="52">
   <si>
     <t>编号</t>
   </si>
@@ -202,6 +202,30 @@
   </si>
   <si>
     <t>投掷闪光弹，致盲范围内所有敌方单位，持续3s，CD：35s</t>
+  </si>
+  <si>
+    <t>突击2</t>
+  </si>
+  <si>
+    <t>治疗2</t>
+  </si>
+  <si>
+    <t>肉盾2</t>
+  </si>
+  <si>
+    <t>功能2</t>
+  </si>
+  <si>
+    <t>突击3</t>
+  </si>
+  <si>
+    <t>治疗3</t>
+  </si>
+  <si>
+    <t>肉盾3</t>
+  </si>
+  <si>
+    <t>功能3</t>
   </si>
 </sst>
 </file>
@@ -1474,60 +1498,274 @@
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:14">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
+      <c r="A8" s="4">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4">
+        <v>4</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="E8" s="4"/>
+      <c r="F8" s="1">
+        <v>100</v>
+      </c>
+      <c r="H8" s="1">
+        <v>15</v>
+      </c>
+      <c r="J8" s="1">
+        <v>15</v>
+      </c>
+      <c r="K8" s="1">
+        <v>50</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:14">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
+      <c r="A9" s="4">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4">
+        <v>5</v>
+      </c>
+      <c r="C9" s="4">
+        <v>1</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="E9" s="4"/>
+      <c r="F9" s="1">
+        <v>100</v>
+      </c>
+      <c r="I9" s="1">
+        <v>20</v>
+      </c>
+      <c r="J9" s="1">
+        <v>8</v>
+      </c>
+      <c r="K9" s="1">
+        <v>40</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:14">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
+      <c r="A10" s="4">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4">
+        <v>6</v>
+      </c>
+      <c r="C10" s="4">
+        <v>2</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="E10" s="4"/>
+      <c r="F10" s="1">
+        <v>100</v>
+      </c>
+      <c r="I10" s="1">
+        <v>15</v>
+      </c>
+      <c r="J10" s="1">
+        <v>2</v>
+      </c>
+      <c r="K10" s="1">
+        <v>30</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:14">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
+      <c r="A11" s="4">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4">
+        <v>7</v>
+      </c>
+      <c r="C11" s="4">
+        <v>3</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>47</v>
+      </c>
       <c r="E11" s="4"/>
+      <c r="F11" s="1">
+        <v>100</v>
+      </c>
+      <c r="J11" s="1">
+        <v>3</v>
+      </c>
+      <c r="K11" s="1">
+        <v>35</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:14">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
+      <c r="A12" s="4">
+        <v>8</v>
+      </c>
+      <c r="B12" s="4">
+        <v>8</v>
+      </c>
+      <c r="C12" s="4">
+        <v>0</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="E12" s="4"/>
+      <c r="F12" s="1">
+        <v>100</v>
+      </c>
+      <c r="H12" s="1">
+        <v>15</v>
+      </c>
+      <c r="J12" s="1">
+        <v>15</v>
+      </c>
+      <c r="K12" s="1">
+        <v>50</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:14">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
+      <c r="A13" s="4">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4">
+        <v>9</v>
+      </c>
+      <c r="C13" s="4">
+        <v>1</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>49</v>
+      </c>
       <c r="E13" s="4"/>
+      <c r="F13" s="1">
+        <v>100</v>
+      </c>
+      <c r="I13" s="1">
+        <v>20</v>
+      </c>
+      <c r="J13" s="1">
+        <v>8</v>
+      </c>
+      <c r="K13" s="1">
+        <v>40</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:14">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
+      <c r="A14" s="4">
+        <v>10</v>
+      </c>
+      <c r="B14" s="4">
+        <v>10</v>
+      </c>
+      <c r="C14" s="4">
+        <v>2</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>50</v>
+      </c>
       <c r="E14" s="4"/>
+      <c r="F14" s="1">
+        <v>100</v>
+      </c>
+      <c r="I14" s="1">
+        <v>15</v>
+      </c>
+      <c r="J14" s="1">
+        <v>2</v>
+      </c>
+      <c r="K14" s="1">
+        <v>30</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:14">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
+      <c r="A15" s="4">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4">
+        <v>11</v>
+      </c>
+      <c r="C15" s="4">
+        <v>3</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>51</v>
+      </c>
       <c r="E15" s="4"/>
+      <c r="F15" s="1">
+        <v>100</v>
+      </c>
+      <c r="J15" s="1">
+        <v>3</v>
+      </c>
+      <c r="K15" s="1">
+        <v>35</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="5"/>

--- a/excel/role.xlsx
+++ b/excel/role.xlsx
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="66">
   <si>
     <t>编号</t>
   </si>
@@ -114,6 +114,9 @@
     <t>主动描述</t>
   </si>
   <si>
+    <t>人物描述</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -156,6 +159,9 @@
     <t>initiativeDesc</t>
   </si>
   <si>
+    <t>infoDesc</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -174,6 +180,9 @@
     <t>开启后角色获得20%加速，击杀敌人时恢复最大生命值20%血量，并延长持续时间3s；技能持续时间15s，CD：50s。</t>
   </si>
   <si>
+    <t>人物描述1</t>
+  </si>
+  <si>
     <t>治疗1</t>
   </si>
   <si>
@@ -186,6 +195,9 @@
     <t>召唤治疗无人机，跟随角色移动，每秒恢复范围内友军最大生命值5%，并对敌人造成最大生命值3%伤害，持续8s；CD：40s。</t>
   </si>
   <si>
+    <t>人物描述2</t>
+  </si>
+  <si>
     <t>肉盾1</t>
   </si>
   <si>
@@ -195,6 +207,9 @@
     <t>召唤能量盾抵挡所有伤害持续2s，CD：30s。</t>
   </si>
   <si>
+    <t>人物描述3</t>
+  </si>
+  <si>
     <t>功能1</t>
   </si>
   <si>
@@ -204,28 +219,55 @@
     <t>投掷闪光弹，致盲范围内所有敌方单位，持续3s，CD：35s</t>
   </si>
   <si>
+    <t>人物描述4</t>
+  </si>
+  <si>
     <t>突击2</t>
   </si>
   <si>
+    <t>人物描述5</t>
+  </si>
+  <si>
     <t>治疗2</t>
   </si>
   <si>
+    <t>人物描述6</t>
+  </si>
+  <si>
     <t>肉盾2</t>
   </si>
   <si>
+    <t>人物描述7</t>
+  </si>
+  <si>
     <t>功能2</t>
   </si>
   <si>
+    <t>人物描述8</t>
+  </si>
+  <si>
     <t>突击3</t>
   </si>
   <si>
+    <t>人物描述9</t>
+  </si>
+  <si>
     <t>治疗3</t>
   </si>
   <si>
+    <t>人物描述10</t>
+  </si>
+  <si>
     <t>肉盾3</t>
   </si>
   <si>
+    <t>人物描述11</t>
+  </si>
+  <si>
     <t>功能3</t>
+  </si>
+  <si>
+    <t>人物描述12</t>
   </si>
 </sst>
 </file>
@@ -1215,7 +1257,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N608"/>
+  <dimension ref="A1:O608"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="5" width="25.125" style="2" customWidth="1"/>
@@ -1224,10 +1266,11 @@
     <col min="12" max="12" width="21.5166666666667" style="2" customWidth="1"/>
     <col min="13" max="13" width="93.8" style="2" customWidth="1"/>
     <col min="14" max="14" width="105.316666666667" style="2" customWidth="1"/>
+    <col min="15" max="15" width="50.6583333333333" customWidth="1"/>
     <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:14">
+    <row r="1" ht="16.5" spans="1:15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1270,96 +1313,105 @@
       <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:14">
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="1:15">
       <c r="A2" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:14">
+        <v>28</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" spans="1:15">
       <c r="A3" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:14">
+        <v>31</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:15">
       <c r="A4" s="4">
         <v>0</v>
       </c>
@@ -1370,7 +1422,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E4" s="4">
         <v>1</v>
@@ -1389,16 +1441,19 @@
         <v>50</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:14">
+        <v>35</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:15">
       <c r="A5" s="4">
         <v>1</v>
       </c>
@@ -1409,7 +1464,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="1">
@@ -1425,16 +1480,19 @@
         <v>40</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:14">
+        <v>40</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:15">
       <c r="A6" s="4">
         <v>2</v>
       </c>
@@ -1445,7 +1503,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="1">
@@ -1461,13 +1519,16 @@
         <v>30</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:14">
+        <v>44</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:15">
       <c r="A7" s="4">
         <v>3</v>
       </c>
@@ -1478,7 +1539,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="1">
@@ -1491,13 +1552,16 @@
         <v>35</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:14">
+        <v>48</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:15">
       <c r="A8" s="4">
         <v>4</v>
       </c>
@@ -1508,7 +1572,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="1">
@@ -1524,16 +1588,19 @@
         <v>50</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:14">
+        <v>35</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:15">
       <c r="A9" s="4">
         <v>5</v>
       </c>
@@ -1544,7 +1611,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="1">
@@ -1560,16 +1627,19 @@
         <v>40</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:14">
+        <v>40</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:15">
       <c r="A10" s="4">
         <v>6</v>
       </c>
@@ -1580,7 +1650,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="1">
@@ -1596,13 +1666,16 @@
         <v>30</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:14">
+        <v>44</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:15">
       <c r="A11" s="4">
         <v>7</v>
       </c>
@@ -1613,7 +1686,7 @@
         <v>3</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="1">
@@ -1626,13 +1699,16 @@
         <v>35</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:14">
+        <v>48</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:15">
       <c r="A12" s="4">
         <v>8</v>
       </c>
@@ -1643,7 +1719,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="1">
@@ -1659,16 +1735,19 @@
         <v>50</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:14">
+        <v>35</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:15">
       <c r="A13" s="4">
         <v>9</v>
       </c>
@@ -1679,7 +1758,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="1">
@@ -1695,16 +1774,19 @@
         <v>40</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:14">
+        <v>40</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:15">
       <c r="A14" s="4">
         <v>10</v>
       </c>
@@ -1715,7 +1797,7 @@
         <v>2</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E14" s="4"/>
       <c r="F14" s="1">
@@ -1731,13 +1813,16 @@
         <v>30</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:14">
+        <v>44</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:15">
       <c r="A15" s="4">
         <v>11</v>
       </c>
@@ -1748,7 +1833,7 @@
         <v>3</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="1">
@@ -1761,13 +1846,16 @@
         <v>35</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+        <v>48</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>

--- a/excel/role.xlsx
+++ b/excel/role.xlsx
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="40">
   <si>
     <t>编号</t>
   </si>
@@ -88,30 +88,6 @@
   </si>
   <si>
     <t>生命值</t>
-  </si>
-  <si>
-    <t>被动持续时间</t>
-  </si>
-  <si>
-    <t>被动冷却时间</t>
-  </si>
-  <si>
-    <t>被动数值</t>
-  </si>
-  <si>
-    <t>主动持续时间</t>
-  </si>
-  <si>
-    <t>主动冷却时间</t>
-  </si>
-  <si>
-    <t>主动数值</t>
-  </si>
-  <si>
-    <t>被动描述</t>
-  </si>
-  <si>
-    <t>主动描述</t>
   </si>
   <si>
     <t>人物描述</t>
@@ -135,30 +111,6 @@
     <t>hp</t>
   </si>
   <si>
-    <t>passiveTime</t>
-  </si>
-  <si>
-    <t>passiveCd</t>
-  </si>
-  <si>
-    <t>passiveValue</t>
-  </si>
-  <si>
-    <t>initiativeTime</t>
-  </si>
-  <si>
-    <t>initiativeCd</t>
-  </si>
-  <si>
-    <t>initiativeValue</t>
-  </si>
-  <si>
-    <t>passiveDesc</t>
-  </si>
-  <si>
-    <t>initiativeDesc</t>
-  </si>
-  <si>
     <t>infoDesc</t>
   </si>
   <si>
@@ -171,28 +123,10 @@
     <t>突击1</t>
   </si>
   <si>
-    <t>[20,20,3]</t>
-  </si>
-  <si>
-    <t>加速替换为滑铲技能（使用滑铲人物向后倾斜并快速向前移动一小段距离）CD：15s。</t>
-  </si>
-  <si>
-    <t>开启后角色获得20%加速，击杀敌人时恢复最大生命值20%血量，并延长持续时间3s；技能持续时间15s，CD：50s。</t>
-  </si>
-  <si>
     <t>人物描述1</t>
   </si>
   <si>
     <t>治疗1</t>
-  </si>
-  <si>
-    <t>[5,3]</t>
-  </si>
-  <si>
-    <t>提升所有治疗效果20%</t>
-  </si>
-  <si>
-    <t>召唤治疗无人机，跟随角色移动，每秒恢复范围内友军最大生命值5%，并对敌人造成最大生命值3%伤害，持续8s；CD：40s。</t>
   </si>
   <si>
     <t>人物描述2</t>
@@ -201,22 +135,10 @@
     <t>肉盾1</t>
   </si>
   <si>
-    <t>减少所有所到来的伤害15%</t>
-  </si>
-  <si>
-    <t>召唤能量盾抵挡所有伤害持续2s，CD：30s。</t>
-  </si>
-  <si>
     <t>人物描述3</t>
   </si>
   <si>
     <t>功能1</t>
-  </si>
-  <si>
-    <t>幸运值增加更容易获得高等级物品</t>
-  </si>
-  <si>
-    <t>投掷闪光弹，致盲范围内所有敌方单位，持续3s，CD：35s</t>
   </si>
   <si>
     <t>人物描述4</t>
@@ -1257,20 +1179,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O608"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:G608"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="5" width="25.125" style="2" customWidth="1"/>
     <col min="6" max="6" width="16.5166666666667" style="2" customWidth="1"/>
-    <col min="7" max="11" width="19.125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="21.5166666666667" style="2" customWidth="1"/>
-    <col min="13" max="13" width="93.8" style="2" customWidth="1"/>
-    <col min="14" max="14" width="105.316666666667" style="2" customWidth="1"/>
-    <col min="15" max="15" width="50.6583333333333" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="2"/>
+    <col min="7" max="7" width="50.6583333333333" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:15">
+    <row r="1" ht="16.5" spans="1:7">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1292,126 +1210,54 @@
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+    </row>
+    <row r="2" ht="16.5" spans="1:7">
+      <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+    </row>
+    <row r="3" ht="16.5" spans="1:7">
+      <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:15">
-      <c r="A2" s="3" t="s">
+      <c r="B3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:15">
-      <c r="A3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="E3" s="3" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:7">
       <c r="A4" s="4">
         <v>0</v>
       </c>
@@ -1422,7 +1268,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E4" s="4">
         <v>1</v>
@@ -1430,30 +1276,11 @@
       <c r="F4" s="1">
         <v>100</v>
       </c>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1">
-        <v>15</v>
-      </c>
-      <c r="J4" s="1">
-        <v>15</v>
-      </c>
-      <c r="K4" s="1">
-        <v>50</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:15">
+      <c r="G4" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:7">
       <c r="A5" s="4">
         <v>1</v>
       </c>
@@ -1464,35 +1291,17 @@
         <v>1</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="1">
         <v>100</v>
       </c>
-      <c r="I5" s="1">
-        <v>20</v>
-      </c>
-      <c r="J5" s="1">
-        <v>8</v>
-      </c>
-      <c r="K5" s="1">
-        <v>40</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:15">
+      <c r="G5" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:7">
       <c r="A6" s="4">
         <v>2</v>
       </c>
@@ -1503,32 +1312,17 @@
         <v>2</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="1">
         <v>100</v>
       </c>
-      <c r="I6" s="1">
-        <v>15</v>
-      </c>
-      <c r="J6" s="1">
-        <v>2</v>
-      </c>
-      <c r="K6" s="1">
-        <v>30</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:15">
+      <c r="G6" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:7">
       <c r="A7" s="4">
         <v>3</v>
       </c>
@@ -1539,29 +1333,17 @@
         <v>3</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="1">
         <v>100</v>
       </c>
-      <c r="J7" s="1">
-        <v>3</v>
-      </c>
-      <c r="K7" s="1">
-        <v>35</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:15">
+      <c r="G7" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:7">
       <c r="A8" s="4">
         <v>4</v>
       </c>
@@ -1572,35 +1354,17 @@
         <v>0</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="1">
         <v>100</v>
       </c>
-      <c r="H8" s="1">
-        <v>15</v>
-      </c>
-      <c r="J8" s="1">
-        <v>15</v>
-      </c>
-      <c r="K8" s="1">
-        <v>50</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:15">
+      <c r="G8" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:7">
       <c r="A9" s="4">
         <v>5</v>
       </c>
@@ -1611,35 +1375,17 @@
         <v>1</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="1">
         <v>100</v>
       </c>
-      <c r="I9" s="1">
-        <v>20</v>
-      </c>
-      <c r="J9" s="1">
-        <v>8</v>
-      </c>
-      <c r="K9" s="1">
-        <v>40</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:15">
+      <c r="G9" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:7">
       <c r="A10" s="4">
         <v>6</v>
       </c>
@@ -1650,32 +1396,17 @@
         <v>2</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="1">
         <v>100</v>
       </c>
-      <c r="I10" s="1">
-        <v>15</v>
-      </c>
-      <c r="J10" s="1">
-        <v>2</v>
-      </c>
-      <c r="K10" s="1">
-        <v>30</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:15">
+      <c r="G10" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:7">
       <c r="A11" s="4">
         <v>7</v>
       </c>
@@ -1686,29 +1417,17 @@
         <v>3</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="1">
         <v>100</v>
       </c>
-      <c r="J11" s="1">
-        <v>3</v>
-      </c>
-      <c r="K11" s="1">
-        <v>35</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:15">
+      <c r="G11" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:7">
       <c r="A12" s="4">
         <v>8</v>
       </c>
@@ -1719,35 +1438,17 @@
         <v>0</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="1">
         <v>100</v>
       </c>
-      <c r="H12" s="1">
-        <v>15</v>
-      </c>
-      <c r="J12" s="1">
-        <v>15</v>
-      </c>
-      <c r="K12" s="1">
-        <v>50</v>
-      </c>
-      <c r="L12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:15">
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:7">
       <c r="A13" s="4">
         <v>9</v>
       </c>
@@ -1758,35 +1459,17 @@
         <v>1</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="1">
         <v>100</v>
       </c>
-      <c r="I13" s="1">
-        <v>20</v>
-      </c>
-      <c r="J13" s="1">
-        <v>8</v>
-      </c>
-      <c r="K13" s="1">
-        <v>40</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:15">
+      <c r="G13" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:7">
       <c r="A14" s="4">
         <v>10</v>
       </c>
@@ -1797,32 +1480,17 @@
         <v>2</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="E14" s="4"/>
       <c r="F14" s="1">
         <v>100</v>
       </c>
-      <c r="I14" s="1">
-        <v>15</v>
-      </c>
-      <c r="J14" s="1">
-        <v>2</v>
-      </c>
-      <c r="K14" s="1">
-        <v>30</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:15">
+      <c r="G14" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:7">
       <c r="A15" s="4">
         <v>11</v>
       </c>
@@ -1833,29 +1501,17 @@
         <v>3</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="1">
         <v>100</v>
       </c>
-      <c r="J15" s="1">
-        <v>3</v>
-      </c>
-      <c r="K15" s="1">
-        <v>35</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+      <c r="G15" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>

--- a/excel/role.xlsx
+++ b/excel/role.xlsx
@@ -1274,7 +1274,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>17</v>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>19</v>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>21</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>23</v>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>25</v>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>27</v>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>29</v>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>31</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>33</v>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>35</v>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="E14" s="4"/>
       <c r="F14" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>37</v>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>39</v>
